--- a/artfynd/A 22024-2020 artfynd.xlsx
+++ b/artfynd/A 22024-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22024-2020 artfynd.xlsx
+++ b/artfynd/A 22024-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5566,6 +5566,127 @@
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>121829526</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90748</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Svenskbyskogen S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>568966</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6621850</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Återfynd.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Bestånd med gammeltallar.</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22024-2020 artfynd.xlsx
+++ b/artfynd/A 22024-2020 artfynd.xlsx
@@ -5571,7 +5571,7 @@
         <v>121829526</v>
       </c>
       <c r="B40" t="n">
-        <v>90748</v>
+        <v>90762</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>

--- a/artfynd/A 22024-2020 artfynd.xlsx
+++ b/artfynd/A 22024-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5687,6 +5687,132 @@
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123308672</v>
+      </c>
+      <c r="B41" t="n">
+        <v>56458</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>svenskbyskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>568905</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6621845</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22024-2020 artfynd.xlsx
+++ b/artfynd/A 22024-2020 artfynd.xlsx
@@ -5692,7 +5692,7 @@
         <v>123308672</v>
       </c>
       <c r="B41" t="n">
-        <v>56458</v>
+        <v>56461</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 22024-2020 artfynd.xlsx
+++ b/artfynd/A 22024-2020 artfynd.xlsx
@@ -5692,7 +5692,7 @@
         <v>123308672</v>
       </c>
       <c r="B41" t="n">
-        <v>56461</v>
+        <v>56467</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 22024-2020 artfynd.xlsx
+++ b/artfynd/A 22024-2020 artfynd.xlsx
@@ -5692,7 +5692,7 @@
         <v>123308672</v>
       </c>
       <c r="B41" t="n">
-        <v>56467</v>
+        <v>56470</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 22024-2020 artfynd.xlsx
+++ b/artfynd/A 22024-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5813,6 +5813,130 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125288571</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57532</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Svenskbyskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>568759</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6622112</v>
+      </c>
+      <c r="S42" t="n">
+        <v>150</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22024-2020 artfynd.xlsx
+++ b/artfynd/A 22024-2020 artfynd.xlsx
@@ -5822,7 +5822,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">

--- a/artfynd/A 22024-2020 artfynd.xlsx
+++ b/artfynd/A 22024-2020 artfynd.xlsx
@@ -5818,7 +5818,7 @@
         <v>125288571</v>
       </c>
       <c r="B42" t="n">
-        <v>57532</v>
+        <v>57629</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 22024-2020 artfynd.xlsx
+++ b/artfynd/A 22024-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5818,12 +5818,7 @@
         <v>125288571</v>
       </c>
       <c r="B42" t="n">
-        <v>57629</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57645</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5936,6 +5931,125 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125865709</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Svenskbyskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>568688</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6621918</v>
+      </c>
+      <c r="S43" t="n">
+        <v>100</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22024-2020 artfynd.xlsx
+++ b/artfynd/A 22024-2020 artfynd.xlsx
@@ -5818,7 +5818,7 @@
         <v>125288571</v>
       </c>
       <c r="B42" t="n">
-        <v>57645</v>
+        <v>57646</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>125865709</v>
       </c>
       <c r="B43" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 22024-2020 artfynd.xlsx
+++ b/artfynd/A 22024-2020 artfynd.xlsx
@@ -5937,7 +5937,7 @@
         <v>125865709</v>
       </c>
       <c r="B43" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 22024-2020 artfynd.xlsx
+++ b/artfynd/A 22024-2020 artfynd.xlsx
@@ -5937,7 +5937,7 @@
         <v>125865709</v>
       </c>
       <c r="B43" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
